--- a/assets/constructions/examples/ctd_tkoi_holder_flat.xlsx
+++ b/assets/constructions/examples/ctd_tkoi_holder_flat.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CV11-0829</t>
+          <t>CV08-0621</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,7 +618,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_MICR:8</t>
+          <t>VAR_MICR:6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -608,24 +628,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>V11</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VARGUS_MHC:8</t>
+          <t>VARGUS_MHC:6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -633,12 +653,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>64.5</v>
+        <v>45</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -673,11 +693,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>13307.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CV08-0621</t>
+          <t>CV11-0829</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -692,7 +726,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VAR_MICR:6</t>
+          <t>VAR_MICR:8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -702,24 +736,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>V08</t>
+          <t>V11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VARGUS_MHC:6</t>
+          <t>VARGUS_MHC:8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>VARGUS_V11</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -727,12 +761,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>45</v>
+        <v>64.5</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -767,6 +801,20 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>174.38</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>16031.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,6 +909,20 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>194.05</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>17839.73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -955,6 +1017,20 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>150.68</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>13852.57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
